--- a/ホームページの詳細設計.xlsx
+++ b/ホームページの詳細設計.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9096" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="9" r:id="rId1"/>
@@ -12,12 +12,15 @@
     <sheet name="詳細" sheetId="4" r:id="rId3"/>
     <sheet name="機能(共通)" sheetId="7" r:id="rId4"/>
     <sheet name="機能(制作物)" sheetId="10" r:id="rId5"/>
-    <sheet name="実装予定の機能" sheetId="5" r:id="rId6"/>
+    <sheet name="実装予定の機能" sheetId="12" r:id="rId6"/>
+    <sheet name="ひな型" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">ひな型!$A$1:$AX$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">概要!$A$1:$AW$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'機能(共通)'!$A$1:$AY$54</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'機能(制作物)'!$A$1:$AY$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'機能(制作物)'!$A$1:$AY$81</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">実装予定の機能!$A$1:$AX$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">詳細!$A$1:$AW$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">目次!$A$1:$AW$34</definedName>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="141">
   <si>
     <t>サイト名</t>
   </si>
@@ -302,9 +305,6 @@
     <t xml:space="preserve">【処理詳細】  </t>
   </si>
   <si>
-    <t xml:space="preserve">1. `DOMContentLoaded` イベントでDOM構築完了を検知  </t>
-  </si>
-  <si>
     <t xml:space="preserve">2. `.menu-toggle` クラスを持つ要素（ボタン）を取得  </t>
   </si>
   <si>
@@ -475,6 +475,147 @@
     <rPh sb="21" eb="22">
       <t>ヒラ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>).&lt;script&gt;...  ...&lt;/script&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. `DOMContentLoaded` イベントでDOM構築完了を検知  (HTMLの読み込みがすべて完了したあとに中の処理を実行するようにしています。)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィルター機能</t>
+    <rPh sb="5" eb="7">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>const checkboxes = document.querySelectorAll('#filter input[type="checkbox"]');</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      </t>
+  </si>
+  <si>
+    <t>const items = document.querySelectorAll('.work-item');</t>
+  </si>
+  <si>
+    <t>checkboxes.forEach(checkbox =&gt; {</t>
+  </si>
+  <si>
+    <t>checkbox.addEventListener('change', () =&gt; {</t>
+  </si>
+  <si>
+    <t>const selected = Array.from(checkboxes)</t>
+  </si>
+  <si>
+    <t>.filter(cb =&gt; cb.checked)</t>
+  </si>
+  <si>
+    <t>.map(cb =&gt; cb.value);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          items.forEach(item =&gt; {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            const category = item.dataset.category;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            item.style.display = selected.includes(category) ? 'block' : 'none';</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          });</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        });</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      });</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    });</t>
+  </si>
+  <si>
+    <t>2. HTML内で、id="filter" の中にある チェックボックス（input type="checkbox"） をすべて取得します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3. .work-item クラスを持つ要素（＝作品や記事など）をすべて取得します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4. すべてのチェックボックスに対して、順番に処理を行います。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5. 各チェックボックスに「状態が変わったとき（チェック or チェック解除）」のイベントを設定します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. ページが読み込まれたら実行。</t>
+  </si>
+  <si>
+    <t>2. チェックボックスをすべて取得。</t>
+  </si>
+  <si>
+    <t>3. 各チェックボックスに「変更されたときの動作」を登録。</t>
+  </si>
+  <si>
+    <t>4. チェックされたカテゴリを調べる。</t>
+  </si>
+  <si>
+    <t>5. .work-item の data-category と一致するものだけを表示する。</t>
+  </si>
+  <si>
+    <t>6. NodeList（配列のようなもの）を本物の配列に変換します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7. 配列の中から「チェックされているものだけ」を取り出します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8. チェックされているボックスの value 属性だけを取り出して、配列にします。["web", "game"]のようになります。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9. 表示対象の .work-item 要素を1つずつ処理します。作品に対して「表示する？隠す？」を判断</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10. 各 .work-item の data-category 属性の値を取得します。例：&lt;div class="work-item" data-category="web"&gt; なら "web" を取得。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【大まかな流れ】  </t>
+    <rPh sb="1" eb="2">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14. checkboxes.forEach(...) の終わり。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13. checkbox.addEventListener('change', ...) の終わり。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12. items.forEach の終わり。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11. selected（チェックされたカテゴリ）に今のアイテムのカテゴリが含まれていれば表示（block）し、含まれていなければ非表示（none）にし、選択されたカテゴリだけが画面に残るようにします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15. 最初の DOMContentLoaded の終わり。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -959,7 +1100,7 @@
         <v>46</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="2:28" ht="19.2" x14ac:dyDescent="0.45">
@@ -971,7 +1112,7 @@
         <v>46</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="2:28" ht="19.2" x14ac:dyDescent="0.45">
@@ -983,7 +1124,7 @@
         <v>46</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:28" ht="19.2" x14ac:dyDescent="0.45">
@@ -995,7 +1136,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="2:28" ht="19.2" x14ac:dyDescent="0.45">
@@ -1007,7 +1148,7 @@
         <v>46</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="2:28" ht="16.2" x14ac:dyDescent="0.2">
@@ -1179,7 +1320,7 @@
     </row>
     <row r="22" spans="1:7" ht="16.2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1190,22 +1331,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1331,50 +1472,50 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1493,57 +1634,57 @@
     </row>
     <row r="16" spans="2:30" x14ac:dyDescent="0.2">
       <c r="D16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G17" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X17" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G18" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X18" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.2">
       <c r="X19" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G20" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="X20" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G21" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X21" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D23" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D24" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="2:24" ht="16.2" x14ac:dyDescent="0.2">
@@ -1671,7 +1812,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AS48"/>
+  <dimension ref="B1:AS75"/>
   <sheetFormatPr defaultColWidth="2.8984375" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.8984375" style="6"/>
@@ -1679,7 +1820,7 @@
     <col min="3" max="16384" width="2.8984375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:45" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J1" s="10" t="str">
         <f>目次!$D$9</f>
         <v>機能(制作物)</v>
@@ -1705,102 +1846,279 @@
       <c r="AC1" s="10"/>
       <c r="AD1" s="10"/>
     </row>
-    <row r="3" spans="2:45" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="5">
         <f>MAX($B$1:B2)+1</f>
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="C4" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="C5" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="D6" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="D7" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE7" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="F8" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE8" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="D9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE9" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="F11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE11" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="G12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE12" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="G13" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE13" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="H14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE14" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="H15" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE15" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="D17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE17" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="4:31" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE18" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="D19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE19" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="D20" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE20" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="D21" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE21" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="D22" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE22" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="D23" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE23" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="D25" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="E26" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="E27" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="E28" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="E29" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="4:31" x14ac:dyDescent="0.2">
+      <c r="E30" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="4:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="2:45" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="5">
+        <f>MAX($B$1:B32)+1</f>
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="C34" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="C4" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="2:45" ht="13.2" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="2:45" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="5">
-        <f>MAX($B$1:B5)+1</f>
-        <v>2</v>
-      </c>
-      <c r="C6" s="5" t="s">
+    <row r="36" spans="2:45" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B36" s="5">
+        <f>MAX($B$1:B35)+1</f>
+        <v>3</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="C37" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="C7" s="6" t="s">
+    <row r="39" spans="2:45" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B39" s="5">
+        <f>MAX($B$1:B38)+1</f>
+        <v>4</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="2:45" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B9" s="5">
-        <f>MAX($B$1:B8)+1</f>
-        <v>3</v>
-      </c>
-      <c r="C9" s="5" t="s">
+    <row r="40" spans="2:45" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B40" s="5"/>
+      <c r="C40" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="10" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="C10" s="6" t="s">
+      <c r="AR40" s="5">
+        <f>MAX($B$1:AR39)+1</f>
+        <v>5</v>
+      </c>
+      <c r="AS40" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:45" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B12" s="5">
-        <f>MAX($B$1:B11)+1</f>
-        <v>4</v>
-      </c>
-      <c r="C12" s="5" t="s">
+    <row r="42" spans="2:45" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B42" s="5">
+        <f>MAX($B$1:B41)+1</f>
+        <v>5</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="C43" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="2:45" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B13" s="5"/>
-      <c r="C13" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AR13" s="5">
-        <f>MAX($B$1:AR12)+1</f>
-        <v>5</v>
-      </c>
-      <c r="AS13" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
-    </row>
-    <row r="30" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B30" s="5"/>
-      <c r="C30" s="7"/>
-    </row>
-    <row r="33" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
-    </row>
-    <row r="36" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B36" s="5"/>
-      <c r="C36" s="7"/>
-    </row>
-    <row r="39" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B39" s="5"/>
-      <c r="C39" s="7"/>
-    </row>
-    <row r="42" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B42" s="5"/>
-      <c r="C42" s="7"/>
-    </row>
-    <row r="45" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B45" s="5"/>
-      <c r="C45" s="7"/>
-    </row>
-    <row r="48" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
-      <c r="B48" s="5"/>
-      <c r="C48" s="7"/>
+    <row r="54" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B54" s="5"/>
+      <c r="C54" s="7"/>
+    </row>
+    <row r="57" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B57" s="5"/>
+      <c r="C57" s="7"/>
+    </row>
+    <row r="60" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B60" s="5"/>
+      <c r="C60" s="7"/>
+    </row>
+    <row r="63" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B63" s="5"/>
+      <c r="C63" s="7"/>
+    </row>
+    <row r="66" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B66" s="5"/>
+      <c r="C66" s="7"/>
+    </row>
+    <row r="69" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B69" s="5"/>
+      <c r="C69" s="7"/>
+    </row>
+    <row r="72" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B72" s="5"/>
+      <c r="C72" s="7"/>
+    </row>
+    <row r="75" spans="2:3" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B75" s="5"/>
+      <c r="C75" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1923,4 +2241,76 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="56" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:AC17"/>
+  <sheetFormatPr defaultColWidth="2.8984375" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="26" width="2.8984375" style="1"/>
+    <col min="27" max="27" width="2.796875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="2.8984375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:29" ht="21" x14ac:dyDescent="0.25">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+    </row>
+    <row r="3" spans="2:29" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B3" s="5"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="8" spans="2:29" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B8" s="5"/>
+    </row>
+    <row r="12" spans="2:29" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B12" s="5"/>
+    </row>
+    <row r="17" spans="2:2" ht="16.2" x14ac:dyDescent="0.2">
+      <c r="B17" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="I1:AC1"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="55" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>